--- a/data/trans_dic/IP11C$nada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria</t>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 69,52</t>
+          <t>8,98; 67,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,32; 84,56</t>
+          <t>9,21; 83,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,42</t>
+          <t>0,0; 84,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 67,28</t>
+          <t>14,6; 68,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 59,1</t>
+          <t>11,45; 57,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,48; 60,24</t>
+          <t>19,61; 60,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,17</t>
+          <t>0,0; 53,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,3</t>
+          <t>0,0; 56,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,54; 83,25</t>
+          <t>27,13; 82,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 83,23</t>
+          <t>13,37; 82,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 61,25</t>
+          <t>10,87; 57,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,13</t>
+          <t>0,0; 58,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,41; 58,75</t>
+          <t>16,76; 58,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,12; 63,02</t>
+          <t>26,67; 63,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,32</t>
+          <t>0,0; 48,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,95</t>
+          <t>0,0; 84,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 78,07</t>
+          <t>10,85; 78,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,9</t>
+          <t>0,0; 45,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,51</t>
+          <t>0,0; 45,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,45</t>
+          <t>0,0; 60,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 46,66</t>
+          <t>5,21; 45,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,24; 51,48</t>
+          <t>11,05; 52,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,57</t>
+          <t>0,0; 46,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 50,51</t>
+          <t>10,41; 51,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,42; 66,74</t>
+          <t>22,55; 64,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,26</t>
+          <t>0,0; 67,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,8</t>
+          <t>0,0; 30,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 39,12</t>
+          <t>10,72; 37,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 40,75</t>
+          <t>4,93; 40,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,93</t>
+          <t>0,0; 53,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 31,0</t>
+          <t>6,81; 30,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,27; 45,9</t>
+          <t>20,41; 44,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 27,62</t>
+          <t>3,01; 25,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,83</t>
+          <t>0,0; 41,31</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 53,06</t>
+          <t>10,3; 52,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,53</t>
+          <t>0,0; 45,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,37</t>
+          <t>0,0; 27,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 44,51</t>
+          <t>5,67; 44,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,44</t>
+          <t>0,0; 38,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,11</t>
+          <t>0,0; 21,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 39,5</t>
+          <t>12,45; 40,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,07</t>
+          <t>0,0; 30,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1427,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,51; 66,01</t>
+          <t>12,37; 62,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,88</t>
+          <t>0,0; 83,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,22; 67,47</t>
+          <t>16,98; 64,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,66</t>
+          <t>0,0; 86,22</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,15; 39,48</t>
+          <t>15,35; 40,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,53; 54,52</t>
+          <t>29,4; 53,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 17,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 31,92</t>
+          <t>3,8; 35,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,45; 25,85</t>
+          <t>8,7; 26,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,13; 34,52</t>
+          <t>18,61; 35,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 26,39</t>
+          <t>8,11; 28,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,13</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,76; 29,18</t>
+          <t>14,6; 29,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,01; 39,9</t>
+          <t>25,59; 39,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,57; 18,72</t>
+          <t>5,73; 18,93</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 16,92</t>
+          <t>1,9; 17,67</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5189</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>526; 3965</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>431; 3892</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3348</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1303; 6105</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2746</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1123; 5664</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2667; 8174</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3676</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4299</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3173</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4030</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7472</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3437</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2090; 6357</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>753; 4645</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1025; 5376</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3444</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1955; 6852</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4568; 10924</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3849</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2782</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2570</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3456</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>676; 4875</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3877</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2775</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3449</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>646; 5578</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1359; 6403</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2969</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3276</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7158</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12583</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1324; 6605</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3575; 10194</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3612</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4485</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2599; 8994</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>608; 4978</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3805</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1855; 8264</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8187; 17754</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>614; 5272</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5152</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1366; 6981</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2995</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3090</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>768; 6028</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3366</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3051</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3335; 10853</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4754</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3240</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2840</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2043</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2375</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1142; 5798</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3420</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1914; 7241</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2522</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>9095</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20980</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2291</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>16547</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>39538</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5231; 13667</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>14630; 26574</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3816</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>652; 6040</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3929; 12141</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>13297; 25531</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3301; 11436</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3557</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>11570; 23699</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>31022; 48047</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3598; 11898</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>781; 7278</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$nada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Clase-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 67,69</t>
+          <t>9,43; 71,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,21; 83,28</t>
+          <t>9,64; 83,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,54</t>
+          <t>0,0; 82,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 68,4</t>
+          <t>14,55; 68,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 57,7</t>
+          <t>12,81; 60,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,61; 60,11</t>
+          <t>19,33; 58,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,22</t>
+          <t>0,0; 54,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,92</t>
+          <t>0,0; 55,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,13; 82,52</t>
+          <t>27,58; 83,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,37; 82,53</t>
+          <t>13,86; 82,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 57,02</t>
+          <t>13,37; 62,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,33</t>
+          <t>0,0; 56,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 58,74</t>
+          <t>11,96; 57,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,67; 63,77</t>
+          <t>26,02; 64,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,3</t>
+          <t>0,0; 49,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,38</t>
+          <t>0,0; 84,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 78,23</t>
+          <t>11,47; 78,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,0</t>
+          <t>0,0; 45,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,69</t>
+          <t>0,0; 52,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,64</t>
+          <t>0,0; 53,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 45,01</t>
+          <t>5,54; 44,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 52,03</t>
+          <t>10,86; 51,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,51</t>
+          <t>0,0; 47,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 51,95</t>
+          <t>9,36; 47,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,55; 64,3</t>
+          <t>25,24; 63,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,9</t>
+          <t>0,0; 59,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,86</t>
+          <t>0,0; 33,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,72; 37,08</t>
+          <t>10,94; 38,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 40,37</t>
+          <t>5,01; 41,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,2</t>
+          <t>0,0; 44,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 30,33</t>
+          <t>7,61; 32,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 44,26</t>
+          <t>19,15; 44,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 25,88</t>
+          <t>3,02; 24,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,31</t>
+          <t>0,0; 35,3</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,3; 52,64</t>
+          <t>9,74; 52,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,45</t>
+          <t>0,0; 53,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,62</t>
+          <t>0,0; 22,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 44,53</t>
+          <t>5,3; 42,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,1</t>
+          <t>0,0; 43,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,72</t>
+          <t>0,0; 17,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 40,5</t>
+          <t>12,32; 38,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,82</t>
+          <t>0,0; 30,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 62,81</t>
+          <t>12,35; 61,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,89</t>
+          <t>0,0; 82,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,98; 64,23</t>
+          <t>18,32; 65,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,22</t>
+          <t>0,0; 86,66</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,35; 40,1</t>
+          <t>16,92; 42,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,4; 53,4</t>
+          <t>31,34; 53,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,25</t>
+          <t>0,0; 21,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 35,21</t>
+          <t>3,94; 33,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,7; 26,88</t>
+          <t>8,9; 27,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,61; 35,73</t>
+          <t>18,03; 34,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,11; 28,08</t>
+          <t>7,52; 26,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,6; 29,9</t>
+          <t>14,32; 28,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,59; 39,64</t>
+          <t>26,3; 39,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 18,93</t>
+          <t>6,28; 20,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,67</t>
+          <t>2,01; 15,96</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>526; 3965</t>
+          <t>552; 4162</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>431; 3892</t>
+          <t>450; 3916</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3348</t>
+          <t>0; 3271</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1303; 6105</t>
+          <t>1299; 6092</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1123; 5664</t>
+          <t>1257; 5893</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2667; 8174</t>
+          <t>2628; 7970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3676</t>
+          <t>0; 3780</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3437</t>
+          <t>0; 3375</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2090; 6357</t>
+          <t>2125; 6403</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>753; 4645</t>
+          <t>780; 4648</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1025; 5376</t>
+          <t>1260; 5930</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3444</t>
+          <t>0; 3363</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2175,17 +2175,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1955; 6852</t>
+          <t>1395; 6694</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4568; 10924</t>
+          <t>4457; 11113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3849</t>
+          <t>0; 3931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3188</t>
+          <t>0; 3190</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>676; 4875</t>
+          <t>715; 4874</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3877</t>
+          <t>0; 3919</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2775</t>
+          <t>0; 3167</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3449</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>646; 5578</t>
+          <t>686; 5534</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1359; 6403</t>
+          <t>1337; 6368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2969</t>
+          <t>0; 3033</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1324; 6605</t>
+          <t>1190; 6030</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3575; 10194</t>
+          <t>4001; 10087</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2566,47 +2566,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 3183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4485</t>
+          <t>0; 4926</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2599; 8994</t>
+          <t>2654; 9433</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>608; 4978</t>
+          <t>618; 5145</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3805</t>
+          <t>0; 3199</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1855; 8264</t>
+          <t>2074; 8933</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8187; 17754</t>
+          <t>7679; 17994</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>614; 5272</t>
+          <t>616; 5051</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 5152</t>
+          <t>0; 4402</t>
         </is>
       </c>
     </row>
@@ -2764,12 +2764,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1366; 6981</t>
+          <t>1292; 7005</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2995</t>
+          <t>0; 3542</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3090</t>
+          <t>0; 2532</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>768; 6028</t>
+          <t>717; 5789</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3366</t>
+          <t>0; 3839</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3051</t>
+          <t>0; 2524</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3335; 10853</t>
+          <t>3302; 10321</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4754</t>
+          <t>0; 4682</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1142; 5798</t>
+          <t>1139; 5715</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3420</t>
+          <t>0; 3354</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1914; 7241</t>
+          <t>2065; 7341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2522</t>
+          <t>0; 2535</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5231; 13667</t>
+          <t>5768; 14365</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14630; 26574</t>
+          <t>15597; 26688</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3816</t>
+          <t>0; 4680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>652; 6040</t>
+          <t>676; 5804</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3929; 12141</t>
+          <t>4019; 12222</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13297; 25531</t>
+          <t>12881; 24564</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3301; 11436</t>
+          <t>3063; 10637</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3557</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11570; 23699</t>
+          <t>11349; 22334</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31022; 48047</t>
+          <t>31882; 48420</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3598; 11898</t>
+          <t>3949; 12821</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>781; 7278</t>
+          <t>829; 6574</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$nada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,37 +649,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37,29%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31,84%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>39,81%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 71,06</t>
+          <t>0,0; 82,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 83,8</t>
+          <t>14,48; 67,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,61</t>
+          <t>8,95; 69,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,55; 68,26</t>
+          <t>9,32; 84,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 60,04</t>
+          <t>13,32; 59,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,33; 58,61</t>
+          <t>18,48; 60,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,72</t>
+          <t>0,0; 57,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -789,37 +789,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>21,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>55,81%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>48,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,88</t>
+          <t>14,11; 83,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,58; 83,12</t>
+          <t>12,08; 61,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 64,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,86; 82,58</t>
+          <t>0,0; 55,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,37; 62,9</t>
+          <t>19,54; 83,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 57,38</t>
+          <t>13,41; 58,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 64,87</t>
+          <t>25,12; 63,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,34</t>
+          <t>0,0; 49,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -929,37 +929,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>34,75%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>44,64%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,44</t>
+          <t>0,0; 38,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 78,21</t>
+          <t>0,0; 48,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 57,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,49</t>
+          <t>0,0; 82,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,13</t>
+          <t>11,37; 78,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 44,66</t>
+          <t>6,31; 46,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,86; 51,75</t>
+          <t>11,24; 51,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,51</t>
+          <t>0,0; 46,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22,37%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>25,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>45,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 47,42</t>
+          <t>0,0; 31,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,24; 63,62</t>
+          <t>11,23; 39,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,9; 40,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,83</t>
+          <t>0,0; 48,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,9</t>
+          <t>10,11; 50,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 38,89</t>
+          <t>26,42; 66,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 41,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,73</t>
+          <t>0,0; 59,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 32,78</t>
+          <t>7,19; 31,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 44,86</t>
+          <t>20,27; 45,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 24,8</t>
+          <t>3,01; 27,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,3</t>
+          <t>0,0; 41,81</t>
         </is>
       </c>
     </row>
@@ -1209,37 +1209,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>26,64%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,2%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 28,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,74; 52,83</t>
+          <t>4,91; 44,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,75</t>
+          <t>0,0; 38,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 42,76</t>
+          <t>8,81; 53,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,45</t>
+          <t>0,0; 44,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,97</t>
+          <t>0,0; 22,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 38,51</t>
+          <t>12,37; 39,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,35</t>
+          <t>0,0; 30,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>47,16%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>65,99%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59,5%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>57,84%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>32,85%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>40,7%</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>32,85%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>40,7%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -1417,52 +1417,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14,51; 66,01</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>12,35; 61,92</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,27</t>
+          <t>0,0; 84,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 65,12</t>
+          <t>18,22; 67,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,66</t>
+          <t>0,0; 86,83</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>26,68%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42,16%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,97%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,92; 42,14</t>
+          <t>8,45; 25,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,34; 53,63</t>
+          <t>18,13; 34,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,15</t>
+          <t>7,45; 26,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 33,84</t>
+          <t>0,0; 13,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,9; 27,06</t>
+          <t>15,15; 39,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,03; 34,38</t>
+          <t>31,53; 54,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 26,12</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>4,12; 33,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,32; 28,18</t>
+          <t>14,76; 29,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,3; 39,95</t>
+          <t>26,01; 39,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 20,4</t>
+          <t>5,57; 18,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 15,96</t>
+          <t>2,28; 17,29</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1859,37 +1859,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1865</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1860</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3328</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>552; 4162</t>
+          <t>0; 3264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>450; 3916</t>
+          <t>1293; 6005</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2746</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3271</t>
+          <t>524; 4072</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1299; 6092</t>
+          <t>436; 3952</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2746</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1257; 5893</t>
+          <t>1307; 5802</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2628; 7970</t>
+          <t>2513; 8191</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3780</t>
+          <t>0; 3949</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1999,37 +1999,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,37 +2067,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3173</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1302</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4299</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3173</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3375</t>
+          <t>794; 4684</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2125; 6403</t>
+          <t>1139; 5775</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3786</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>780; 4648</t>
+          <t>0; 3340</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1260; 5930</t>
+          <t>1506; 6414</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3363</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2175,17 +2175,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1395; 6694</t>
+          <t>1565; 6854</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4457; 11113</t>
+          <t>4303; 10797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3931</t>
+          <t>0; 3930</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2212,32 +2212,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2275,37 +2275,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1313</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2782</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3190</t>
+          <t>0; 3352</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>715; 4874</t>
+          <t>0; 2947</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3268</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3919</t>
+          <t>0; 3134</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3167</t>
+          <t>708; 4865</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>686; 5534</t>
+          <t>782; 5783</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1337; 6368</t>
+          <t>1383; 6335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3033</t>
+          <t>0; 2973</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2415,37 +2415,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2483,62 +2483,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3276</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7158</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1470</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5425</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12583</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>2075</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4746</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>12583</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1505</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1190; 6030</t>
+          <t>0; 4621</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4001; 10087</t>
+          <t>2725; 9489</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>605; 5025</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3183</t>
+          <t>0; 3108</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4926</t>
+          <t>1286; 6422</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2654; 9433</t>
+          <t>4189; 10581</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>618; 5145</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3199</t>
+          <t>0; 3100</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2074; 8933</t>
+          <t>1959; 8448</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7679; 17994</t>
+          <t>8131; 18412</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>616; 5051</t>
+          <t>614; 5626</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4402</t>
+          <t>0; 4847</t>
         </is>
       </c>
     </row>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2691,37 +2691,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>3532</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>738</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2718</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3175</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1292; 7005</t>
+          <t>664; 6026</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3542</t>
+          <t>0; 3396</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2532</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>717; 5789</t>
+          <t>1168; 7036</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3839</t>
+          <t>0; 2935</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2524</t>
+          <t>0; 3106</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3302; 10321</t>
+          <t>3315; 10584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4682</t>
+          <t>0; 4638</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,34 +2899,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3240</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1348</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3240</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1490</t>
         </is>
       </c>
     </row>
@@ -2967,34 +2967,34 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1340; 6093</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2840</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>0; 2043</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2375</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1139; 5715</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -3002,17 +3002,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2577</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3354</t>
+          <t>0; 3461</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2065; 7341</t>
+          <t>2054; 7606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2535</t>
+          <t>0; 2633</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>9095</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>20980</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2291</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7452</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>18558</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2996</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5768; 14365</t>
+          <t>3818; 11676</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15597; 26688</t>
+          <t>12951; 24662</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4680</t>
+          <t>3033; 10746</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>676; 5804</t>
+          <t>0; 2912</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4019; 12222</t>
+          <t>5165; 13458</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12881; 24564</t>
+          <t>15690; 27131</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3063; 10637</t>
+          <t>0; 3439</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>707; 5701</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11349; 22334</t>
+          <t>11697; 23123</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31882; 48420</t>
+          <t>31528; 48370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3949; 12821</t>
+          <t>3503; 11766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>829; 6574</t>
+          <t>900; 6818</t>
         </is>
       </c>
     </row>
